--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.beta.carotenes/Resultats_total.beta.carotenes_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.beta.carotenes/Resultats_total.beta.carotenes_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.4088503790867671</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.583914181880967</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.6361260768522069</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.663813803317489</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.6974472840003365</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.7171223033755669</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.7423583333238937</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.7498631811137266</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.7679656973244243</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.7756391833561503</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.793942958611039</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.8075578792196957</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.8352015500910895</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.8694378192903849</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.879742885114717</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.5010704083431416</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.579352768736878</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.6143626024790588</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.657868053278029</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.6925270510836572</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.7300124495273507</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.7527982273496805</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.7751552328538366</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.7849334744081103</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.8004602372675611</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.8158059018179601</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8330024931786837</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8581483567706486</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8697544738585538</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8835180597410562</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.4242584452169479</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.5637353764622266</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.5903975230959486</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.63117830528462</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.7003602709759844</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.7193348340256073</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.735851249639083</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.7418786968906552</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.7657067572083781</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.7936654107770186</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.8337375679064843</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.8488030291896291</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.8655020739078867</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.8737580408068333</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.8840765716325788</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.5628622210647664</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.5921885274023824</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.6469759219322747</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.6751256822347915</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.726565745472747</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.7357203121739273</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.7561388721529563</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.771402022539397</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.7868833090942917</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.8046678846071357</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.8270029066998839</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.8550231827312121</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.872917849943982</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8915987075261184</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.9046507953753434</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.5637446681590771</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.5919757818650102</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.6346299315599587</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.6721751880399649</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.7265117325658668</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.7355828020177569</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.7468497009381729</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.7623174993535949</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.7790957963412102</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.7912543787892528</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.8171629748833109</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.8373532490619234</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8690760785063938</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8786213652151177</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8861088771878173</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.4240294910706216</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.5777026289925343</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.6725867740172735</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.6952390050467896</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.725544812606768</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.7357090864329425</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.7560264344532697</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.768237863476343</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.7736735780912241</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.7955241821271638</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.8158614508442094</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.8386012279223469</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.8572422544044829</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.8739174972184665</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.8827090997342979</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.4754421831507382</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.558795698579113</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.6465834694724633</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.6801675679157463</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.6930520006075611</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.7386885850627827</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.7477376571572978</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.7578843875800112</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.7706758732859855</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.7921658101361112</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.8217363585830335</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.8360879419678673</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8517666453787902</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.8622871853324857</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.8714439760387118</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.4754070407717859</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.5587495429290339</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.6459388400240512</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.6778821016651195</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.6894028664788121</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.7308067294822687</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.7385913145386092</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.7469322212374543</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.753519161220027</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.7623569598468144</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.7807686701222094</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.7936573979662993</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.8024123834346375</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.8121343596288029</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.8190366722560266</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.4753698814988672</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.5587401283987521</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.6459392086048554</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.6778731465959297</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.6893404185496279</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.7304385205476427</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.7382217635679149</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.746540914578814</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.7530315571196027</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.7614326452428777</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.7798745727147434</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.7919100814017208</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.7987127401039513</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.8074222017636372</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.8139452725419186</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.4754071196999584</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.5587368344683858</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.6460059166432441</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.6781045244338193</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.6896823271894079</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.7312185147357162</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.7388619659642109</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.7470116300496041</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.7534794135234485</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.762115201050328</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.7797662344198741</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.7944387052481071</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.8025955603631805</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.8114647797976989</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.81983735881052</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.5733151882447255</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.6089076240565138</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.6789391235670679</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.7046350308733617</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.7395797926174097</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.758339316288155</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.7720368887564418</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.7809830182688716</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.7928163882172561</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.8096553986269353</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.8257256023903063</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.8467026223622267</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.8547010975305096</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.8718922342338962</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8849994058676844</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.5731270517710031</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.6185589024611362</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.6779676362556454</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.6982344433241532</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.7329165047881449</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.7585196935259398</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.7779901727363161</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.7930718408706499</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.8092375927725989</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.8254685537947746</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.8331248328300427</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.8401228175751484</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8502832649666525</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.8604431676972093</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.8695760709749868</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.4240219294543296</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.5776672943649712</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.6724046060412422</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.694906869383799</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.7244829154056698</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.7340004779254095</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.7528842448736812</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.7622825217303412</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.7660741839786118</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.7799718449554159</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.7894830644549815</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.8060807054020906</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.820875993959767</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.8304762485058544</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.8355448341451566</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.4239973613154417</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.5776755311251043</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.6723889666359332</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.6948673467703641</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.724223637220031</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.7335847894374949</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.7521591742400708</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.7610620206545464</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.764782625749229</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.777849414966335</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.7859554248707709</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.8004365856921247</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.8153233170931823</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.8251200120451426</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.8302253222709359</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.4239663685521429</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.5776846730277225</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.6723672133584255</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.694833831244301</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.7241139833459569</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.7334200195534003</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.751919945456847</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.7609035004386702</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.7646089724493198</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.7772459042211716</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.7847149628812505</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.7984183860938849</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.812094249568162</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.8212224672047834</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.8262350255692726</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.4238882310811788</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.5776867596610504</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.6722940161469004</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.6947522407452131</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.7238616104556328</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.7330589890568512</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.751369900322832</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.7605693176204145</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.7644405256264977</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7771382036202936</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.7844595808758701</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.7982903298810812</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.811161572568291</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.8199956142901035</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.8261207846085421</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.5754035944090343</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.6111970738856849</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.6762202138835136</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.7025506924727406</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.7461222761810302</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.7656282729231101</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.771980352593843</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.7871194356844698</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.7996482984548168</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.8209174861424873</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.8413343226491912</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.8679670401800279</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8786538635945618</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.8940728987336598</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.9090004065984912</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.5765172822327178</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.6110648973165984</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.6591451431399014</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.6973326881380573</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.7387209808264837</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.7497975386600495</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.7589094198756329</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.7744386731067164</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.7898005216783679</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.8095047008925678</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.8337749792053415</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.8455382886384716</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.86244116487364</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8717097687168003</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8838184059751593</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.5766156488603036</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.6114294796943196</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.6654695426903526</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.724065988347148</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.7361044870264288</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.7492325607879106</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.7549639660354882</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.7668176079435918</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.780106911225078</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.7972367783054507</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.8207970038468014</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.8400148925064679</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.8522668854836849</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8641871646681862</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8782573349499698</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.4996425605985553</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.5764323258995698</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.6105088812590062</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.6617336509868925</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.7045112710387862</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.739993601327968</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.7557119823994014</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.7763884676977468</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.7894814057649802</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.8166250357058376</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.8269394992794843</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8412695217918221</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.8620741727644734</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.8719053691145175</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.8830692949356531</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.4987707533104682</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.5757156615352721</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.6062512943013525</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.657291787617077</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.7096015947851673</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.7314846669590159</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.7600543663615493</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.7723786231713327</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.7914481185296931</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.8142604255225302</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.8277312802678016</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8519099263831622</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8664607156547148</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8755960027805046</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.8891781986920202</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.5695449120651893</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.5989566493594867</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.6533813844641532</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.6678478246254967</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.6872467903534299</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.7263169628155925</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.7461783520876064</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7701477638159984</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.7931555552374524</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8247388835289036</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8470466117440539</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.8635960640001772</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8832231144138387</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.9007995721958991</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9164386775647446</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.222238981709193</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.3166083058950058</v>
+        <v>0.6157464702559232</v>
       </c>
       <c r="D24">
-        <v>0.3520240614211405</v>
+        <v>0.6846448425112734</v>
       </c>
       <c r="E24">
-        <v>0.3660944048504451</v>
+        <v>0.7234576780242709</v>
       </c>
       <c r="F24">
-        <v>0.4620276496626083</v>
+        <v>0.7480257506347419</v>
       </c>
       <c r="G24">
-        <v>0.5083153335270254</v>
+        <v>0.7680835147219305</v>
       </c>
       <c r="H24">
-        <v>0.5776041200972593</v>
+        <v>0.7841365074770528</v>
       </c>
       <c r="I24">
-        <v>0.6137721487958057</v>
+        <v>0.7927394681256441</v>
       </c>
       <c r="J24">
-        <v>0.6597405875888689</v>
+        <v>0.8154694104036475</v>
       </c>
       <c r="K24">
-        <v>0.6931084124311959</v>
+        <v>0.8326082631059207</v>
       </c>
       <c r="L24">
-        <v>0.7242081311790212</v>
+        <v>0.8572735351036689</v>
       </c>
       <c r="M24">
-        <v>0.7591524915079432</v>
+        <v>0.8788914483399195</v>
       </c>
       <c r="N24">
-        <v>0.8147760762665371</v>
+        <v>0.8974414731326298</v>
       </c>
       <c r="O24">
-        <v>0.841528023685834</v>
+        <v>0.9094239721572653</v>
       </c>
       <c r="P24">
-        <v>0.8636458816763684</v>
+        <v>0.9239032696619018</v>
+      </c>
+      <c r="Q24">
+        <v>0.9346054766988333</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.2052335877097579</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.2870675658404167</v>
+        <v>0.6152784823892032</v>
       </c>
       <c r="D25">
-        <v>0.3284896757339052</v>
+        <v>0.6881880649281538</v>
       </c>
       <c r="E25">
-        <v>0.4087134412367928</v>
+        <v>0.7423408006002696</v>
       </c>
       <c r="F25">
-        <v>0.4908819479709198</v>
+        <v>0.7746114150385591</v>
       </c>
       <c r="G25">
-        <v>0.5410363234475102</v>
+        <v>0.8008195694788225</v>
       </c>
       <c r="H25">
-        <v>0.5723768432658954</v>
+        <v>0.8121074170322989</v>
       </c>
       <c r="I25">
-        <v>0.6209844684912247</v>
+        <v>0.8151379968275974</v>
       </c>
       <c r="J25">
-        <v>0.6560779295180769</v>
+        <v>0.8476628765849146</v>
       </c>
       <c r="K25">
-        <v>0.6953972762020026</v>
+        <v>0.8541155541978438</v>
       </c>
       <c r="L25">
-        <v>0.7491267759087804</v>
+        <v>0.8792927270076101</v>
       </c>
       <c r="M25">
-        <v>0.8018779637368969</v>
+        <v>0.8935013784300951</v>
       </c>
       <c r="N25">
-        <v>0.8347000435371774</v>
+        <v>0.9033825185185966</v>
       </c>
       <c r="O25">
-        <v>0.854174808052151</v>
+        <v>0.9190238150605099</v>
       </c>
       <c r="P25">
-        <v>0.8710850624973256</v>
+        <v>0.9261643081494119</v>
+      </c>
+      <c r="Q25">
+        <v>0.9400325557618808</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.189936104636872</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.2533467321231905</v>
+        <v>0.6320509917675707</v>
       </c>
       <c r="D26">
-        <v>0.2899376576368584</v>
+        <v>0.672952168014589</v>
       </c>
       <c r="E26">
-        <v>0.3317684788269363</v>
+        <v>0.7389759795166191</v>
       </c>
       <c r="F26">
-        <v>0.3811481287922857</v>
+        <v>0.7729257764639386</v>
       </c>
       <c r="G26">
-        <v>0.4136983399962118</v>
+        <v>0.7843831586341616</v>
       </c>
       <c r="H26">
-        <v>0.4420513980075867</v>
+        <v>0.7984490182190085</v>
       </c>
       <c r="I26">
-        <v>0.4927787435668344</v>
+        <v>0.8092346133056549</v>
       </c>
       <c r="J26">
-        <v>0.5349317460539673</v>
+        <v>0.8257526185608812</v>
       </c>
       <c r="K26">
-        <v>0.5796592333237833</v>
+        <v>0.8593690946268923</v>
       </c>
       <c r="L26">
-        <v>0.6086619174736411</v>
+        <v>0.8836469892288756</v>
       </c>
       <c r="M26">
-        <v>0.6423433949837623</v>
+        <v>0.9044003691481122</v>
       </c>
       <c r="N26">
-        <v>0.6736843021252108</v>
+        <v>0.914753134929622</v>
       </c>
       <c r="O26">
-        <v>0.7118488641199112</v>
+        <v>0.9215239836737144</v>
       </c>
       <c r="P26">
-        <v>0.7351425033348088</v>
+        <v>0.9360460397454694</v>
+      </c>
+      <c r="Q26">
+        <v>0.9434313879596353</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.168004033374675</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.2274242124705442</v>
+        <v>0.6320121462335159</v>
       </c>
       <c r="D27">
-        <v>0.3608640917280481</v>
+        <v>0.6727552845907407</v>
       </c>
       <c r="E27">
-        <v>0.3750706125182189</v>
+        <v>0.7384089249676409</v>
       </c>
       <c r="F27">
-        <v>0.4382623041973875</v>
+        <v>0.7704653819702832</v>
       </c>
       <c r="G27">
-        <v>0.4925317531677014</v>
+        <v>0.7822282228117178</v>
       </c>
       <c r="H27">
-        <v>0.5399524903832795</v>
+        <v>0.7942749075796507</v>
       </c>
       <c r="I27">
-        <v>0.5704832459987033</v>
+        <v>0.8011537012421587</v>
       </c>
       <c r="J27">
-        <v>0.6325379832046649</v>
+        <v>0.8098062350733458</v>
       </c>
       <c r="K27">
-        <v>0.6510279261766905</v>
+        <v>0.8191002025040366</v>
       </c>
       <c r="L27">
-        <v>0.6645979255988436</v>
+        <v>0.8261664955647641</v>
       </c>
       <c r="M27">
-        <v>0.717709597595432</v>
+        <v>0.8324485024548882</v>
       </c>
       <c r="N27">
-        <v>0.739759072368039</v>
+        <v>0.840703496263006</v>
       </c>
       <c r="O27">
-        <v>0.780003239684805</v>
+        <v>0.8446886872174501</v>
       </c>
       <c r="P27">
-        <v>0.7965400685407116</v>
+        <v>0.8557925759241799</v>
+      </c>
+      <c r="Q27">
+        <v>0.8655704991155142</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.6157464702559232</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.6846448425112734</v>
+        <v>0.6151929658301545</v>
       </c>
       <c r="D28">
-        <v>0.7234576780242709</v>
+        <v>0.6880556849587669</v>
       </c>
       <c r="E28">
-        <v>0.7480257506347419</v>
+        <v>0.7418059763324123</v>
       </c>
       <c r="F28">
-        <v>0.7680835147219305</v>
+        <v>0.7741911253486768</v>
       </c>
       <c r="G28">
-        <v>0.7841365074770528</v>
+        <v>0.7994907629536632</v>
       </c>
       <c r="H28">
-        <v>0.7927394681256441</v>
+        <v>0.8091787028661334</v>
       </c>
       <c r="I28">
-        <v>0.8154694104036475</v>
+        <v>0.8111043659900209</v>
       </c>
       <c r="J28">
-        <v>0.8326082631059207</v>
+        <v>0.8290320312687401</v>
       </c>
       <c r="K28">
-        <v>0.8572735351036689</v>
+        <v>0.8319808040105735</v>
       </c>
       <c r="L28">
-        <v>0.8788914483399195</v>
+        <v>0.8383263613655169</v>
       </c>
       <c r="M28">
-        <v>0.8974414731326298</v>
+        <v>0.8422410257932702</v>
       </c>
       <c r="N28">
-        <v>0.9094239721572653</v>
+        <v>0.8474606266316191</v>
       </c>
       <c r="O28">
-        <v>0.9239032696619018</v>
+        <v>0.8505204014022484</v>
       </c>
       <c r="P28">
-        <v>0.9346054766988333</v>
+        <v>0.855310542115973</v>
+      </c>
+      <c r="Q28">
+        <v>0.8619782472520763</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.6152784823892032</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.6881880649281538</v>
+        <v>0.6151017785488606</v>
       </c>
       <c r="D29">
-        <v>0.7423408006002696</v>
+        <v>0.6880433964598858</v>
       </c>
       <c r="E29">
-        <v>0.7746114150385591</v>
+        <v>0.7416557110932438</v>
       </c>
       <c r="F29">
-        <v>0.8008195694788225</v>
+        <v>0.7741704571238579</v>
       </c>
       <c r="G29">
-        <v>0.8121074170322989</v>
+        <v>0.7994061367105622</v>
       </c>
       <c r="H29">
-        <v>0.8151379968275974</v>
+        <v>0.8089468734532148</v>
       </c>
       <c r="I29">
-        <v>0.8476628765849146</v>
+        <v>0.8107953302869815</v>
       </c>
       <c r="J29">
-        <v>0.8541155541978438</v>
+        <v>0.8278883781307989</v>
       </c>
       <c r="K29">
-        <v>0.8792927270076101</v>
+        <v>0.8310042124454118</v>
       </c>
       <c r="L29">
-        <v>0.8935013784300951</v>
+        <v>0.8367969759520464</v>
       </c>
       <c r="M29">
-        <v>0.9033825185185966</v>
+        <v>0.8401102565552441</v>
       </c>
       <c r="N29">
-        <v>0.9190238150605099</v>
+        <v>0.8439973760819568</v>
       </c>
       <c r="O29">
-        <v>0.9261643081494119</v>
+        <v>0.8464609416078618</v>
       </c>
       <c r="P29">
-        <v>0.9400325557618808</v>
+        <v>0.8500151319443333</v>
+      </c>
+      <c r="Q29">
+        <v>0.8543156611270579</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.6320509917675707</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.672952168014589</v>
+        <v>0.6150397855561862</v>
       </c>
       <c r="D30">
-        <v>0.7389759795166191</v>
+        <v>0.6880502975636278</v>
       </c>
       <c r="E30">
-        <v>0.7729257764639386</v>
+        <v>0.741571185216102</v>
       </c>
       <c r="F30">
-        <v>0.7843831586341616</v>
+        <v>0.7741561925787599</v>
       </c>
       <c r="G30">
-        <v>0.7984490182190085</v>
+        <v>0.7993599143825044</v>
       </c>
       <c r="H30">
-        <v>0.8092346133056549</v>
+        <v>0.8088334335755798</v>
       </c>
       <c r="I30">
-        <v>0.8257526185608812</v>
+        <v>0.8106454288350722</v>
       </c>
       <c r="J30">
-        <v>0.8593690946268923</v>
+        <v>0.8273135323062889</v>
       </c>
       <c r="K30">
-        <v>0.8836469892288756</v>
+        <v>0.8306004888917571</v>
       </c>
       <c r="L30">
-        <v>0.9044003691481122</v>
+        <v>0.8363723327100634</v>
       </c>
       <c r="M30">
-        <v>0.914753134929622</v>
+        <v>0.8398090991494609</v>
       </c>
       <c r="N30">
-        <v>0.9215239836737144</v>
+        <v>0.8427986885090674</v>
       </c>
       <c r="O30">
-        <v>0.9360460397454694</v>
+        <v>0.8450197498754642</v>
       </c>
       <c r="P30">
-        <v>0.9434313879596353</v>
+        <v>0.8480995724292798</v>
+      </c>
+      <c r="Q30">
+        <v>0.8512450817374536</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.6320121462335159</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.6727552845907407</v>
+        <v>0.614882125176659</v>
       </c>
       <c r="D31">
-        <v>0.7384089249676409</v>
+        <v>0.6880552228006718</v>
       </c>
       <c r="E31">
-        <v>0.7704653819702832</v>
+        <v>0.7413586637346052</v>
       </c>
       <c r="F31">
-        <v>0.7822282228117178</v>
+        <v>0.7741534392750845</v>
       </c>
       <c r="G31">
-        <v>0.7942749075796507</v>
+        <v>0.7993154567982075</v>
       </c>
       <c r="H31">
-        <v>0.8011537012421587</v>
+        <v>0.8086309217112353</v>
       </c>
       <c r="I31">
-        <v>0.8098062350733458</v>
+        <v>0.8103737881112326</v>
       </c>
       <c r="J31">
-        <v>0.8191002025040366</v>
+        <v>0.8261739305925642</v>
       </c>
       <c r="K31">
-        <v>0.8261664955647641</v>
+        <v>0.8299700560829055</v>
       </c>
       <c r="L31">
-        <v>0.8324485024548882</v>
+        <v>0.8361888452628666</v>
       </c>
       <c r="M31">
-        <v>0.840703496263006</v>
+        <v>0.8414227947880721</v>
       </c>
       <c r="N31">
-        <v>0.8446886872174501</v>
+        <v>0.844041099575928</v>
       </c>
       <c r="O31">
-        <v>0.8557925759241799</v>
+        <v>0.8452557274970968</v>
       </c>
       <c r="P31">
-        <v>0.8655704991155142</v>
+        <v>0.8486167538031918</v>
+      </c>
+      <c r="Q31">
+        <v>0.8525194772894963</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.6151929658301545</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.6880556849587669</v>
+        <v>0.6152623947815663</v>
       </c>
       <c r="D32">
-        <v>0.7418059763324123</v>
+        <v>0.6880709736279932</v>
       </c>
       <c r="E32">
-        <v>0.7741911253486768</v>
+        <v>0.74198466607089</v>
       </c>
       <c r="F32">
-        <v>0.7994907629536632</v>
+        <v>0.7742556626375927</v>
       </c>
       <c r="G32">
-        <v>0.8091787028661334</v>
+        <v>0.79965661500037</v>
       </c>
       <c r="H32">
-        <v>0.8111043659900209</v>
+        <v>0.809487580447156</v>
       </c>
       <c r="I32">
-        <v>0.8290320312687401</v>
+        <v>0.8115354604127299</v>
       </c>
       <c r="J32">
-        <v>0.8319808040105735</v>
+        <v>0.8307325730233754</v>
       </c>
       <c r="K32">
-        <v>0.8383263613655169</v>
+        <v>0.8337569264470809</v>
       </c>
       <c r="L32">
-        <v>0.8422410257932702</v>
+        <v>0.8417331247012108</v>
       </c>
       <c r="M32">
-        <v>0.8474606266316191</v>
+        <v>0.8482579772917715</v>
       </c>
       <c r="N32">
-        <v>0.8505204014022484</v>
+        <v>0.8553088297767875</v>
       </c>
       <c r="O32">
-        <v>0.855310542115973</v>
+        <v>0.8595163582119402</v>
       </c>
       <c r="P32">
-        <v>0.8619782472520763</v>
+        <v>0.8650474950492588</v>
+      </c>
+      <c r="Q32">
+        <v>0.8728198349630258</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.6151017785488606</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.6880433964598858</v>
+        <v>0.6152461719018658</v>
       </c>
       <c r="D33">
-        <v>0.7416557110932438</v>
+        <v>0.6880676109138286</v>
       </c>
       <c r="E33">
-        <v>0.7741704571238579</v>
+        <v>0.7419471410894041</v>
       </c>
       <c r="F33">
-        <v>0.7994061367105622</v>
+        <v>0.7742386893670752</v>
       </c>
       <c r="G33">
-        <v>0.8089468734532148</v>
+        <v>0.7995923267317802</v>
       </c>
       <c r="H33">
-        <v>0.8107953302869815</v>
+        <v>0.8093499481619532</v>
       </c>
       <c r="I33">
-        <v>0.8278883781307989</v>
+        <v>0.8113649831456899</v>
       </c>
       <c r="J33">
-        <v>0.8310042124454118</v>
+        <v>0.830147640598208</v>
       </c>
       <c r="K33">
-        <v>0.8367969759520464</v>
+        <v>0.8331072040648098</v>
       </c>
       <c r="L33">
-        <v>0.8401102565552441</v>
+        <v>0.8403297031560871</v>
       </c>
       <c r="M33">
-        <v>0.8439973760819568</v>
+        <v>0.845850071653143</v>
       </c>
       <c r="N33">
-        <v>0.8464609416078618</v>
+        <v>0.8527709524351424</v>
       </c>
       <c r="O33">
-        <v>0.8500151319443333</v>
+        <v>0.8566126004482193</v>
       </c>
       <c r="P33">
-        <v>0.8543156611270579</v>
+        <v>0.861736088485755</v>
+      </c>
+      <c r="Q33">
+        <v>0.8680583892061944</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.6150397855561862</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.6880502975636278</v>
+        <v>0.6152234703010061</v>
       </c>
       <c r="D34">
-        <v>0.741571185216102</v>
+        <v>0.6880706806019338</v>
       </c>
       <c r="E34">
-        <v>0.7741561925787599</v>
+        <v>0.7418968867959261</v>
       </c>
       <c r="F34">
-        <v>0.7993599143825044</v>
+        <v>0.7742131502418572</v>
       </c>
       <c r="G34">
-        <v>0.8088334335755798</v>
+        <v>0.7995319968485441</v>
       </c>
       <c r="H34">
-        <v>0.8106454288350722</v>
+        <v>0.8092319014398289</v>
       </c>
       <c r="I34">
-        <v>0.8273135323062889</v>
+        <v>0.8112176545409826</v>
       </c>
       <c r="J34">
-        <v>0.8306004888917571</v>
+        <v>0.8296286659012689</v>
       </c>
       <c r="K34">
-        <v>0.8363723327100634</v>
+        <v>0.8325902074777184</v>
       </c>
       <c r="L34">
-        <v>0.8398090991494609</v>
+        <v>0.8392153594914902</v>
       </c>
       <c r="M34">
-        <v>0.8427986885090674</v>
+        <v>0.8442072350126327</v>
       </c>
       <c r="N34">
-        <v>0.8450197498754642</v>
+        <v>0.8506323025142596</v>
       </c>
       <c r="O34">
-        <v>0.8480995724292798</v>
+        <v>0.8544292565008645</v>
       </c>
       <c r="P34">
-        <v>0.8512450817374536</v>
+        <v>0.859374293666904</v>
+      </c>
+      <c r="Q34">
+        <v>0.8650079580741074</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.614882125176659</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.6880552228006718</v>
+        <v>0.6151934078563159</v>
       </c>
       <c r="D35">
-        <v>0.7413586637346052</v>
+        <v>0.6880824518590156</v>
       </c>
       <c r="E35">
-        <v>0.7741534392750845</v>
+        <v>0.7418474808521888</v>
       </c>
       <c r="F35">
-        <v>0.7993154567982075</v>
+        <v>0.7741805611995091</v>
       </c>
       <c r="G35">
-        <v>0.8086309217112353</v>
+        <v>0.7994671201558539</v>
       </c>
       <c r="H35">
-        <v>0.8103737881112326</v>
+        <v>0.809101449841938</v>
       </c>
       <c r="I35">
-        <v>0.8261739305925642</v>
+        <v>0.8110649276176035</v>
       </c>
       <c r="J35">
-        <v>0.8299700560829055</v>
+        <v>0.829041084848581</v>
       </c>
       <c r="K35">
-        <v>0.8361888452628666</v>
+        <v>0.8320257385285823</v>
       </c>
       <c r="L35">
-        <v>0.8414227947880721</v>
+        <v>0.8382002640562648</v>
       </c>
       <c r="M35">
-        <v>0.844041099575928</v>
+        <v>0.8427876006700554</v>
       </c>
       <c r="N35">
-        <v>0.8452557274970968</v>
+        <v>0.8482363848959983</v>
       </c>
       <c r="O35">
-        <v>0.8486167538031918</v>
+        <v>0.8518000678139729</v>
       </c>
       <c r="P35">
-        <v>0.8525194772894963</v>
+        <v>0.856795735068705</v>
+      </c>
+      <c r="Q35">
+        <v>0.8623729412407937</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.6152623947815663</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.6880709736279932</v>
+        <v>0.6148879174393722</v>
       </c>
       <c r="D36">
-        <v>0.74198466607089</v>
+        <v>0.6881093432904655</v>
       </c>
       <c r="E36">
-        <v>0.7742556626375927</v>
+        <v>0.7413330575065242</v>
       </c>
       <c r="F36">
-        <v>0.79965661500037</v>
+        <v>0.7740493764555588</v>
       </c>
       <c r="G36">
-        <v>0.809487580447156</v>
+        <v>0.799272687115794</v>
       </c>
       <c r="H36">
-        <v>0.8115354604127299</v>
+        <v>0.8085532954591697</v>
       </c>
       <c r="I36">
-        <v>0.8307325730233754</v>
+        <v>0.8103728300455133</v>
       </c>
       <c r="J36">
-        <v>0.8337569264470809</v>
+        <v>0.8261554465221386</v>
       </c>
       <c r="K36">
-        <v>0.8417331247012108</v>
+        <v>0.8299719820098885</v>
       </c>
       <c r="L36">
-        <v>0.8482579772917715</v>
+        <v>0.8362829434464839</v>
       </c>
       <c r="M36">
-        <v>0.8553088297767875</v>
+        <v>0.8406130711105295</v>
       </c>
       <c r="N36">
-        <v>0.8595163582119402</v>
+        <v>0.8428738958472377</v>
       </c>
       <c r="O36">
-        <v>0.8650474950492588</v>
+        <v>0.8450531169795064</v>
       </c>
       <c r="P36">
-        <v>0.8728198349630258</v>
+        <v>0.8488376894375083</v>
+      </c>
+      <c r="Q36">
+        <v>0.8519015062003427</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.6152461719018658</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.6880676109138286</v>
+        <v>0.6316966448852068</v>
       </c>
       <c r="D37">
-        <v>0.7419471410894041</v>
+        <v>0.7300097248267132</v>
       </c>
       <c r="E37">
-        <v>0.7742386893670752</v>
+        <v>0.7674909994056075</v>
       </c>
       <c r="F37">
-        <v>0.7995923267317802</v>
+        <v>0.7888424895499004</v>
       </c>
       <c r="G37">
-        <v>0.8093499481619532</v>
+        <v>0.8042713698809181</v>
       </c>
       <c r="H37">
-        <v>0.8113649831456899</v>
+        <v>0.8380841753454298</v>
       </c>
       <c r="I37">
-        <v>0.830147640598208</v>
+        <v>0.8558179034065229</v>
       </c>
       <c r="J37">
-        <v>0.8331072040648098</v>
+        <v>0.8655577875982691</v>
       </c>
       <c r="K37">
-        <v>0.8403297031560871</v>
+        <v>0.875217908882837</v>
       </c>
       <c r="L37">
-        <v>0.845850071653143</v>
+        <v>0.8914025805243426</v>
       </c>
       <c r="M37">
-        <v>0.8527709524351424</v>
+        <v>0.9023447434245779</v>
       </c>
       <c r="N37">
-        <v>0.8566126004482193</v>
+        <v>0.9094991563414522</v>
       </c>
       <c r="O37">
-        <v>0.861736088485755</v>
+        <v>0.920221587636626</v>
       </c>
       <c r="P37">
-        <v>0.8680583892061944</v>
+        <v>0.9269511882950094</v>
+      </c>
+      <c r="Q37">
+        <v>0.9310128212937396</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.6152234703010061</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.6880706806019338</v>
+        <v>0.6324292619101913</v>
       </c>
       <c r="D38">
-        <v>0.7418968867959261</v>
+        <v>0.7280960367290331</v>
       </c>
       <c r="E38">
-        <v>0.7742131502418572</v>
+        <v>0.7627060465813241</v>
       </c>
       <c r="F38">
-        <v>0.7995319968485441</v>
+        <v>0.7766676656123535</v>
       </c>
       <c r="G38">
-        <v>0.8092319014398289</v>
+        <v>0.7863738136248423</v>
       </c>
       <c r="H38">
-        <v>0.8112176545409826</v>
+        <v>0.815005995875872</v>
       </c>
       <c r="I38">
-        <v>0.8296286659012689</v>
+        <v>0.8275691005879362</v>
       </c>
       <c r="J38">
-        <v>0.8325902074777184</v>
+        <v>0.8351207350046124</v>
       </c>
       <c r="K38">
-        <v>0.8392153594914902</v>
+        <v>0.8445616853521412</v>
       </c>
       <c r="L38">
-        <v>0.8442072350126327</v>
+        <v>0.8541978968299879</v>
       </c>
       <c r="M38">
-        <v>0.8506323025142596</v>
+        <v>0.8657984471979234</v>
       </c>
       <c r="N38">
-        <v>0.8544292565008645</v>
+        <v>0.8716672530464187</v>
       </c>
       <c r="O38">
-        <v>0.859374293666904</v>
+        <v>0.885994727457261</v>
       </c>
       <c r="P38">
-        <v>0.8650079580741074</v>
+        <v>0.8994873738724537</v>
+      </c>
+      <c r="Q38">
+        <v>0.9093675557414597</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.6151934078563159</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.6880824518590156</v>
+        <v>0.6329287714035883</v>
       </c>
       <c r="D39">
-        <v>0.7418474808521888</v>
+        <v>0.7292212075944455</v>
       </c>
       <c r="E39">
-        <v>0.7741805611995091</v>
+        <v>0.7605217150463798</v>
       </c>
       <c r="F39">
-        <v>0.7994671201558539</v>
+        <v>0.7747978652057241</v>
       </c>
       <c r="G39">
-        <v>0.809101449841938</v>
+        <v>0.7836718854401769</v>
       </c>
       <c r="H39">
-        <v>0.8110649276176035</v>
+        <v>0.8063824636892368</v>
       </c>
       <c r="I39">
-        <v>0.829041084848581</v>
+        <v>0.8155578662586026</v>
       </c>
       <c r="J39">
-        <v>0.8320257385285823</v>
+        <v>0.8204063153171826</v>
       </c>
       <c r="K39">
-        <v>0.8382002640562648</v>
+        <v>0.8277808826927466</v>
       </c>
       <c r="L39">
-        <v>0.8427876006700554</v>
+        <v>0.8369847884045157</v>
       </c>
       <c r="M39">
-        <v>0.8482363848959983</v>
+        <v>0.8403424051924695</v>
       </c>
       <c r="N39">
-        <v>0.8518000678139729</v>
+        <v>0.857376812965795</v>
       </c>
       <c r="O39">
-        <v>0.856795735068705</v>
+        <v>0.8658816060005099</v>
       </c>
       <c r="P39">
-        <v>0.8623729412407937</v>
+        <v>0.8822291171999942</v>
+      </c>
+      <c r="Q39">
+        <v>0.8957785720705153</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.6148879174393722</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.6881093432904655</v>
+        <v>0.5941906142272309</v>
       </c>
       <c r="D40">
-        <v>0.7413330575065242</v>
+        <v>0.6199373889291152</v>
       </c>
       <c r="E40">
-        <v>0.7740493764555588</v>
+        <v>0.6666779867715943</v>
       </c>
       <c r="F40">
-        <v>0.799272687115794</v>
+        <v>0.7194042677542094</v>
       </c>
       <c r="G40">
-        <v>0.8085532954591697</v>
+        <v>0.7771945291003578</v>
       </c>
       <c r="H40">
-        <v>0.8103728300455133</v>
+        <v>0.802215444392873</v>
       </c>
       <c r="I40">
-        <v>0.8261554465221386</v>
+        <v>0.8178144584632111</v>
       </c>
       <c r="J40">
-        <v>0.8299719820098885</v>
+        <v>0.8266266378521097</v>
       </c>
       <c r="K40">
-        <v>0.8362829434464839</v>
+        <v>0.8375710213803016</v>
       </c>
       <c r="L40">
-        <v>0.8406130711105295</v>
+        <v>0.8508813093765039</v>
       </c>
       <c r="M40">
-        <v>0.8428738958472377</v>
+        <v>0.8652841308521522</v>
       </c>
       <c r="N40">
-        <v>0.8450531169795064</v>
+        <v>0.8791925751398747</v>
       </c>
       <c r="O40">
-        <v>0.8488376894375083</v>
+        <v>0.8902768902251887</v>
       </c>
       <c r="P40">
-        <v>0.8519015062003427</v>
+        <v>0.9040304341478282</v>
+      </c>
+      <c r="Q40">
+        <v>0.9137824987784211</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.6316966448852068</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.7300097248267132</v>
+        <v>0.5781690982623333</v>
       </c>
       <c r="D41">
-        <v>0.7674909994056075</v>
+        <v>0.6308503390987206</v>
       </c>
       <c r="E41">
-        <v>0.7888424895499004</v>
+        <v>0.6724946764156711</v>
       </c>
       <c r="F41">
-        <v>0.8042713698809181</v>
+        <v>0.7150719262095695</v>
       </c>
       <c r="G41">
-        <v>0.8380841753454298</v>
+        <v>0.7746853378826258</v>
       </c>
       <c r="H41">
-        <v>0.8558179034065229</v>
+        <v>0.812231560394523</v>
       </c>
       <c r="I41">
-        <v>0.8655577875982691</v>
+        <v>0.827152414931651</v>
       </c>
       <c r="J41">
-        <v>0.875217908882837</v>
+        <v>0.8412432967275838</v>
       </c>
       <c r="K41">
-        <v>0.8914025805243426</v>
+        <v>0.8608581482815304</v>
       </c>
       <c r="L41">
-        <v>0.9023447434245779</v>
+        <v>0.8744425547655992</v>
       </c>
       <c r="M41">
-        <v>0.9094991563414522</v>
+        <v>0.892397498051087</v>
       </c>
       <c r="N41">
-        <v>0.920221587636626</v>
+        <v>0.9085139398766912</v>
       </c>
       <c r="O41">
-        <v>0.9269511882950094</v>
+        <v>0.9286998009474328</v>
       </c>
       <c r="P41">
-        <v>0.9310128212937396</v>
+        <v>0.9426098868424946</v>
+      </c>
+      <c r="Q41">
+        <v>0.9499539743511312</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.6324292619101913</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.7280960367290331</v>
+        <v>0.5150645456816441</v>
       </c>
       <c r="D42">
-        <v>0.7627060465813241</v>
+        <v>0.6052061906764716</v>
       </c>
       <c r="E42">
-        <v>0.7766676656123535</v>
+        <v>0.653198585721242</v>
       </c>
       <c r="F42">
-        <v>0.7863738136248423</v>
+        <v>0.6973207615423576</v>
       </c>
       <c r="G42">
-        <v>0.815005995875872</v>
+        <v>0.7638624661032219</v>
       </c>
       <c r="H42">
-        <v>0.8275691005879362</v>
+        <v>0.7778819655192739</v>
       </c>
       <c r="I42">
-        <v>0.8351207350046124</v>
+        <v>0.7998896573076804</v>
       </c>
       <c r="J42">
-        <v>0.8445616853521412</v>
+        <v>0.8256163894240131</v>
       </c>
       <c r="K42">
-        <v>0.8541978968299879</v>
+        <v>0.841210343439564</v>
       </c>
       <c r="L42">
-        <v>0.8657984471979234</v>
+        <v>0.8654748410414856</v>
       </c>
       <c r="M42">
-        <v>0.8716672530464187</v>
+        <v>0.8841598322989177</v>
       </c>
       <c r="N42">
-        <v>0.885994727457261</v>
+        <v>0.9102309436189115</v>
       </c>
       <c r="O42">
-        <v>0.8994873738724537</v>
+        <v>0.9182487247259403</v>
       </c>
       <c r="P42">
-        <v>0.9093675557414597</v>
+        <v>0.9276529561170497</v>
+      </c>
+      <c r="Q42">
+        <v>0.9365312776405836</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.6329287714035883</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.7292212075944455</v>
+        <v>0.5989151176339198</v>
       </c>
       <c r="D43">
-        <v>0.7605217150463798</v>
+        <v>0.6407222971950176</v>
       </c>
       <c r="E43">
-        <v>0.7747978652057241</v>
+        <v>0.6671948662635945</v>
       </c>
       <c r="F43">
-        <v>0.7836718854401769</v>
+        <v>0.7044117166019503</v>
       </c>
       <c r="G43">
-        <v>0.8063824636892368</v>
+        <v>0.7797456923163557</v>
       </c>
       <c r="H43">
-        <v>0.8155578662586026</v>
+        <v>0.8119258584437137</v>
       </c>
       <c r="I43">
-        <v>0.8204063153171826</v>
+        <v>0.8341431571177895</v>
       </c>
       <c r="J43">
-        <v>0.8277808826927466</v>
+        <v>0.8534366509902819</v>
       </c>
       <c r="K43">
-        <v>0.8369847884045157</v>
+        <v>0.880500825732767</v>
       </c>
       <c r="L43">
-        <v>0.8403424051924695</v>
+        <v>0.9046866275830393</v>
       </c>
       <c r="M43">
-        <v>0.857376812965795</v>
+        <v>0.9190872671433018</v>
       </c>
       <c r="N43">
-        <v>0.8658816060005099</v>
+        <v>0.9297183319265592</v>
       </c>
       <c r="O43">
-        <v>0.8822291171999942</v>
+        <v>0.9374641972462521</v>
       </c>
       <c r="P43">
-        <v>0.8957785720705153</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.5941906142272309</v>
-      </c>
-      <c r="C44">
-        <v>0.6199373889291152</v>
-      </c>
-      <c r="D44">
-        <v>0.6666779867715943</v>
-      </c>
-      <c r="E44">
-        <v>0.7194042677542094</v>
-      </c>
-      <c r="F44">
-        <v>0.7771945291003578</v>
-      </c>
-      <c r="G44">
-        <v>0.802215444392873</v>
-      </c>
-      <c r="H44">
-        <v>0.8178144584632111</v>
-      </c>
-      <c r="I44">
-        <v>0.8266266378521097</v>
-      </c>
-      <c r="J44">
-        <v>0.8375710213803016</v>
-      </c>
-      <c r="K44">
-        <v>0.8508813093765039</v>
-      </c>
-      <c r="L44">
-        <v>0.8652841308521522</v>
-      </c>
-      <c r="M44">
-        <v>0.8791925751398747</v>
-      </c>
-      <c r="N44">
-        <v>0.8902768902251887</v>
-      </c>
-      <c r="O44">
-        <v>0.9040304341478282</v>
-      </c>
-      <c r="P44">
-        <v>0.9137824987784211</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.5781690982623333</v>
-      </c>
-      <c r="C45">
-        <v>0.6308503390987206</v>
-      </c>
-      <c r="D45">
-        <v>0.6724946764156711</v>
-      </c>
-      <c r="E45">
-        <v>0.7150719262095695</v>
-      </c>
-      <c r="F45">
-        <v>0.7746853378826258</v>
-      </c>
-      <c r="G45">
-        <v>0.812231560394523</v>
-      </c>
-      <c r="H45">
-        <v>0.827152414931651</v>
-      </c>
-      <c r="I45">
-        <v>0.8412432967275838</v>
-      </c>
-      <c r="J45">
-        <v>0.8608581482815304</v>
-      </c>
-      <c r="K45">
-        <v>0.8744425547655992</v>
-      </c>
-      <c r="L45">
-        <v>0.892397498051087</v>
-      </c>
-      <c r="M45">
-        <v>0.9085139398766912</v>
-      </c>
-      <c r="N45">
-        <v>0.9286998009474328</v>
-      </c>
-      <c r="O45">
-        <v>0.9426098868424946</v>
-      </c>
-      <c r="P45">
-        <v>0.9499539743511312</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.5150645456816441</v>
-      </c>
-      <c r="C46">
-        <v>0.6052061906764716</v>
-      </c>
-      <c r="D46">
-        <v>0.653198585721242</v>
-      </c>
-      <c r="E46">
-        <v>0.6973207615423576</v>
-      </c>
-      <c r="F46">
-        <v>0.7638624661032219</v>
-      </c>
-      <c r="G46">
-        <v>0.7778819655192739</v>
-      </c>
-      <c r="H46">
-        <v>0.7998896573076804</v>
-      </c>
-      <c r="I46">
-        <v>0.8256163894240131</v>
-      </c>
-      <c r="J46">
-        <v>0.841210343439564</v>
-      </c>
-      <c r="K46">
-        <v>0.8654748410414856</v>
-      </c>
-      <c r="L46">
-        <v>0.8841598322989177</v>
-      </c>
-      <c r="M46">
-        <v>0.9102309436189115</v>
-      </c>
-      <c r="N46">
-        <v>0.9182487247259403</v>
-      </c>
-      <c r="O46">
-        <v>0.9276529561170497</v>
-      </c>
-      <c r="P46">
-        <v>0.9365312776405836</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.5989151176339198</v>
-      </c>
-      <c r="C47">
-        <v>0.6407222971950176</v>
-      </c>
-      <c r="D47">
-        <v>0.6671948662635945</v>
-      </c>
-      <c r="E47">
-        <v>0.7044117166019503</v>
-      </c>
-      <c r="F47">
-        <v>0.7797456923163557</v>
-      </c>
-      <c r="G47">
-        <v>0.8119258584437137</v>
-      </c>
-      <c r="H47">
-        <v>0.8341431571177895</v>
-      </c>
-      <c r="I47">
-        <v>0.8534366509902819</v>
-      </c>
-      <c r="J47">
-        <v>0.880500825732767</v>
-      </c>
-      <c r="K47">
-        <v>0.9046866275830393</v>
-      </c>
-      <c r="L47">
-        <v>0.9190872671433018</v>
-      </c>
-      <c r="M47">
-        <v>0.9297183319265592</v>
-      </c>
-      <c r="N47">
-        <v>0.9374641972462521</v>
-      </c>
-      <c r="O47">
         <v>0.9465571983324397</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.9575094974599022</v>
       </c>
     </row>
